--- a/Data/FlightPlan/FPL_25OCT26.xlsx
+++ b/Data/FlightPlan/FPL_25OCT26.xlsx
@@ -620,13 +620,16 @@
     <t>VN-A549</t>
   </si>
   <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
     <t>10:45</t>
   </si>
   <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>08:05</t>
+    <t>11:35</t>
   </si>
   <si>
     <t>14:15</t>
@@ -785,9 +788,6 @@
     <t>VN-A632</t>
   </si>
   <si>
-    <t>11:35</t>
-  </si>
-  <si>
     <t>16:15</t>
   </si>
   <si>
@@ -1241,7 +1241,7 @@
     <t>Total Record(s): 355</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 25, 2026 05:38</t>
+    <t xml:space="preserve">Generated on  Oct 25, 2026 05:52</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5047,7 +5047,7 @@
         <v>13</v>
       </c>
       <c r="B112" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c t="s" r="C112" s="7">
         <v>14</v>
@@ -5060,27 +5060,31 @@
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H112" s="8">
         <v>48</v>
       </c>
-      <c t="s" r="H112" s="8">
-        <v>31</v>
-      </c>
       <c t="s" r="I112" s="7">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>203</v>
-      </c>
-      <c r="K112" s="7"/>
+        <v>204</v>
+      </c>
+      <c t="s" r="K112" s="7">
+        <v>189</v>
+      </c>
       <c r="L112" s="7"/>
-      <c r="M112" s="7"/>
+      <c t="s" r="M112" s="7">
+        <v>76</v>
+      </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c t="s" r="A113" s="6">
         <v>13</v>
       </c>
       <c r="B113" s="7">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c t="s" r="C113" s="7">
         <v>14</v>
@@ -5093,23 +5097,23 @@
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
+        <v>48</v>
+      </c>
+      <c t="s" r="H113" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H113" s="8">
-        <v>48</v>
-      </c>
       <c t="s" r="I113" s="7">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>205</v>
       </c>
       <c t="s" r="K113" s="7">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5136,7 +5140,7 @@
         <v>171</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>175</v>
@@ -5172,7 +5176,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5199,7 +5203,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="I116" s="7">
         <v>96</v>
@@ -5229,7 +5233,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>31</v>
@@ -5238,7 +5242,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5271,7 +5275,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5283,7 +5287,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>61</v>
@@ -5304,7 +5308,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5316,10 +5320,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5337,7 +5341,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5349,7 +5353,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>90</v>
@@ -5370,7 +5374,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5403,7 +5407,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5436,7 +5440,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5451,7 +5455,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5469,7 +5473,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5484,7 +5488,7 @@
         <v>178</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5502,7 +5506,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5517,7 +5521,7 @@
         <v>195</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5535,7 +5539,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5550,7 +5554,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5583,7 +5587,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5595,7 +5599,7 @@
         <v>63</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>190</v>
@@ -5616,7 +5620,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5649,7 +5653,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5658,13 +5662,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="I131" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5682,13 +5686,13 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>16</v>
@@ -5730,7 +5734,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5742,7 +5746,7 @@
         <v>126</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>147</v>
@@ -5763,7 +5767,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5778,7 +5782,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5796,7 +5800,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5829,7 +5833,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5877,22 +5881,22 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5910,7 +5914,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5943,7 +5947,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5958,7 +5962,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5976,7 +5980,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5988,7 +5992,7 @@
         <v>192</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>99</v>
@@ -6009,7 +6013,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6057,7 +6061,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6090,7 +6094,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6099,13 +6103,13 @@
         <v>22</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="I146" s="7">
         <v>89</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6123,13 +6127,13 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>22</v>
@@ -6156,7 +6160,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6189,7 +6193,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6204,7 +6208,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6222,7 +6226,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6237,7 +6241,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6270,7 +6274,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6285,7 +6289,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6303,7 +6307,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6315,7 +6319,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>130</v>
@@ -6336,7 +6340,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6345,10 +6349,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>19</v>
@@ -6369,13 +6373,13 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>16</v>
@@ -6384,7 +6388,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6402,7 +6406,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6431,11 +6435,11 @@
         <v>6844</v>
       </c>
       <c t="s" r="C157" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6447,10 +6451,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6464,11 +6468,11 @@
         <v>6844</v>
       </c>
       <c t="s" r="C158" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6477,13 +6481,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="I158" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6497,26 +6501,26 @@
         <v>6845</v>
       </c>
       <c t="s" r="C159" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6549,13 +6553,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>16</v>
@@ -6564,7 +6568,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6582,7 +6586,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6591,13 +6595,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>165</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6615,22 +6619,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6663,7 +6667,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6675,7 +6679,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>105</v>
@@ -6696,7 +6700,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6729,7 +6733,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6762,7 +6766,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6771,7 +6775,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>41</v>
@@ -6795,22 +6799,22 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
+        <v>256</v>
+      </c>
+      <c t="s" r="H169" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I169" s="7">
+        <v>257</v>
+      </c>
+      <c t="s" r="J169" s="7">
         <v>255</v>
-      </c>
-      <c t="s" r="H169" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I169" s="7">
-        <v>256</v>
-      </c>
-      <c t="s" r="J169" s="7">
-        <v>254</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6843,7 +6847,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6876,7 +6880,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6909,7 +6913,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6918,10 +6922,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>174</v>
@@ -6942,13 +6946,13 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>31</v>
@@ -6975,7 +6979,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7008,7 +7012,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7041,7 +7045,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7056,7 +7060,7 @@
         <v>261</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7074,7 +7078,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7089,7 +7093,7 @@
         <v>262</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7107,7 +7111,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7266,7 +7270,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>269</v>
@@ -7283,7 +7287,7 @@
         <v>6293</v>
       </c>
       <c t="s" r="C185" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
@@ -7316,7 +7320,7 @@
         <v>6294</v>
       </c>
       <c t="s" r="C186" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
@@ -7446,7 +7450,7 @@
         <v>275</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>276</v>
@@ -7559,7 +7563,7 @@
       </c>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7641,7 +7645,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7671,7 +7675,7 @@
         <v>198</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>194</v>
@@ -7917,7 +7921,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>182</v>
@@ -7998,7 +8002,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>190</v>
@@ -8184,7 +8188,7 @@
         <v>199</v>
       </c>
       <c t="s" r="K214" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
@@ -8428,7 +8432,7 @@
         <v>263</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>186</v>
@@ -8461,7 +8465,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>300</v>
@@ -8608,7 +8612,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>303</v>
@@ -8656,7 +8660,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>305</v>
@@ -8692,14 +8696,14 @@
         <v>106</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="K231" s="7">
         <v>106</v>
       </c>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -8919,7 +8923,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>314</v>
@@ -9186,7 +9190,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9216,7 +9220,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>318</v>
@@ -9348,7 +9352,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>200</v>
@@ -9381,17 +9385,17 @@
         <v>31</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="K253" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9466,7 +9470,7 @@
         <v>126</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>129</v>
@@ -9613,7 +9617,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>156</v>
@@ -9679,10 +9683,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="K263" s="7">
         <v>64</v>
@@ -9750,7 +9754,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>289</v>
@@ -9763,7 +9767,7 @@
       </c>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9784,7 +9788,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>16</v>
@@ -9830,7 +9834,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="K267" s="7">
         <v>154</v>
@@ -9867,7 +9871,7 @@
         <v>195</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="K268" s="7">
         <v>278</v>
@@ -10132,7 +10136,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10165,7 +10169,7 @@
         <v>326</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10243,7 +10247,7 @@
         <v>171</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>328</v>
@@ -10309,7 +10313,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>156</v>
@@ -10596,10 +10600,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10647,7 +10651,7 @@
         <v>334</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10679,7 +10683,7 @@
         <v>163</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>336</v>
@@ -10748,7 +10752,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10790,7 +10794,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>328</v>
@@ -10820,7 +10824,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>31</v>
@@ -10922,7 +10926,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="I303" s="7">
         <v>42</v>
@@ -10952,7 +10956,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>31</v>
@@ -11024,7 +11028,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>341</v>
@@ -11066,7 +11070,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>31</v>
@@ -11185,7 +11189,7 @@
         <v>111</v>
       </c>
       <c t="s" r="K311" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
@@ -11250,7 +11254,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>346</v>
@@ -11334,7 +11338,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>42</v>
@@ -11484,7 +11488,7 @@
         <v>294</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11646,7 +11650,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>87</v>
@@ -11829,7 +11833,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12024,7 +12028,7 @@
         <v>361</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="K339" s="7">
         <v>362</v>
@@ -12250,7 +12254,7 @@
         <v>192</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>117</v>
@@ -12286,7 +12290,7 @@
         <v>324</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12460,7 +12464,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>72</v>
@@ -12490,7 +12494,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>16</v>
@@ -12592,7 +12596,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>42</v>
@@ -12626,7 +12630,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>16</v>
@@ -12724,7 +12728,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12760,7 +12764,7 @@
         <v>288</v>
       </c>
       <c t="s" r="K362" s="7">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
@@ -12908,10 +12912,10 @@
         <v>163</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>174</v>
@@ -12938,7 +12942,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>163</v>
@@ -13046,7 +13050,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13124,7 +13128,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>337</v>
@@ -13452,7 +13456,7 @@
         <v>339</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>375</v>
@@ -13499,7 +13503,7 @@
       </c>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -13544,7 +13548,7 @@
         <v>351</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13736,7 +13740,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13766,13 +13770,13 @@
         <v>48</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="K394" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
@@ -13813,7 +13817,7 @@
       </c>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14020,7 +14024,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>50</v>
@@ -14336,14 +14340,14 @@
         <v>107</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="K413" s="7">
         <v>107</v>
       </c>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -14447,14 +14451,14 @@
         <v>65</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="K416" s="7">
         <v>65</v>
       </c>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14576,11 +14580,11 @@
         <v>288</v>
       </c>
       <c t="s" r="K420" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14639,7 +14643,7 @@
         <v>6874</v>
       </c>
       <c t="s" r="C423" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
@@ -14672,7 +14676,7 @@
         <v>6852</v>
       </c>
       <c t="s" r="C424" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
@@ -14739,7 +14743,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14772,7 +14776,7 @@
         <v>186</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>

--- a/Data/FlightPlan/FPL_25OCT26.xlsx
+++ b/Data/FlightPlan/FPL_25OCT26.xlsx
@@ -536,6 +536,9 @@
     <t>18:30</t>
   </si>
   <si>
+    <t>19:39</t>
+  </si>
+  <si>
     <t>THD</t>
   </si>
   <si>
@@ -599,772 +602,787 @@
     <t>17:50</t>
   </si>
   <si>
+    <t>19:09</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:23</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>14:09</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>16:48</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>17:16</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>17:22</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>11:31</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>15:01</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>12:09</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>12:58</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>17:07</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:28</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>14:31</t>
+  </si>
+  <si>
+    <t>16:03</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:33</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>17:41</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>09:11</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>15:47</t>
+  </si>
+  <si>
+    <t>18:12</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>TNN</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>17:18</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>02:25</t>
+  </si>
+  <si>
+    <t>04:40</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>14:57</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>18:56</t>
+  </si>
+  <si>
+    <t>02:50</t>
+  </si>
+  <si>
+    <t>03:45</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>16:33</t>
+  </si>
+  <si>
+    <t>18:29</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>CNX</t>
+  </si>
+  <si>
+    <t>17:51</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>11:57</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>13:43</t>
+  </si>
+  <si>
+    <t>18:37</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>17:19</t>
+  </si>
+  <si>
+    <t>20:09</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:49</t>
+  </si>
+  <si>
+    <t>929 *</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>14:12</t>
+  </si>
+  <si>
+    <t>928 *</t>
+  </si>
+  <si>
+    <t>19:18</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:29</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>01:50</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>15:41</t>
+  </si>
+  <si>
+    <t>18:02</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>16:28</t>
+  </si>
+  <si>
+    <t>19:11</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>20:22</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>14:24</t>
+  </si>
+  <si>
+    <t>18:21</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>23:21</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>15:19</t>
+  </si>
+  <si>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>18:07</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>12:22</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>14:54</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>11:08</t>
+  </si>
+  <si>
+    <t>13:21</t>
+  </si>
+  <si>
+    <t>15:51</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>12:49</t>
+  </si>
+  <si>
+    <t>16:19</t>
+  </si>
+  <si>
     <t>18:55</t>
   </si>
   <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:23</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:04</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>14:09</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>16:48</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>14:23</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>17:16</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>14:01</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>11:09</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>17:22</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>11:31</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>15:01</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>12:09</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>13:49</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>12:58</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>08:52</t>
-  </si>
-  <si>
-    <t>12:48</t>
-  </si>
-  <si>
-    <t>17:07</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>08:28</t>
-  </si>
-  <si>
-    <t>11:01</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>14:31</t>
-  </si>
-  <si>
-    <t>16:03</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>13:36</t>
-  </si>
-  <si>
-    <t>17:41</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>09:11</t>
-  </si>
-  <si>
-    <t>13:09</t>
-  </si>
-  <si>
-    <t>15:47</t>
-  </si>
-  <si>
-    <t>18:12</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>TNN</t>
-  </si>
-  <si>
-    <t>11:19</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>17:18</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>02:25</t>
-  </si>
-  <si>
-    <t>04:40</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>14:57</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>18:56</t>
-  </si>
-  <si>
-    <t>02:50</t>
-  </si>
-  <si>
-    <t>03:45</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>16:33</t>
-  </si>
-  <si>
-    <t>18:29</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>CNX</t>
-  </si>
-  <si>
-    <t>17:51</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>14:47</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>13:43</t>
-  </si>
-  <si>
-    <t>18:37</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>17:19</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:49</t>
-  </si>
-  <si>
-    <t>929 *</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>14:12</t>
-  </si>
-  <si>
-    <t>928 *</t>
-  </si>
-  <si>
-    <t>19:18</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>13:59</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:29</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>01:50</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>10:37</t>
-  </si>
-  <si>
-    <t>15:41</t>
-  </si>
-  <si>
-    <t>18:02</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>11:07</t>
-  </si>
-  <si>
-    <t>16:28</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>20:22</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>12:08</t>
-  </si>
-  <si>
-    <t>14:24</t>
-  </si>
-  <si>
-    <t>18:21</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>16:46</t>
-  </si>
-  <si>
-    <t>23:21</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>18:23</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>08:56</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>15:19</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>13:56</t>
-  </si>
-  <si>
-    <t>18:07</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:28</t>
-  </si>
-  <si>
-    <t>12:22</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>14:54</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>11:08</t>
-  </si>
-  <si>
-    <t>13:21</t>
-  </si>
-  <si>
-    <t>15:51</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>12:49</t>
-  </si>
-  <si>
-    <t>16:19</t>
+    <t>19:16</t>
   </si>
   <si>
     <t>00:50</t>
@@ -1397,6 +1415,9 @@
     <t>16:43</t>
   </si>
   <si>
+    <t>18:58</t>
+  </si>
+  <si>
     <t>VN-A672</t>
   </si>
   <si>
@@ -1625,7 +1646,7 @@
     <t>Total Record(s): 355</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 25, 2026 17:18</t>
+    <t xml:space="preserve">Generated on  Oct 25, 2026 18:02</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4075,7 +4096,7 @@
       </c>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>25</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -4099,20 +4120,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J66" s="7">
+        <v>178</v>
+      </c>
+      <c t="s" r="K66" s="7">
         <v>177</v>
-      </c>
-      <c t="s" r="K66" s="7">
-        <v>176</v>
       </c>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -4133,7 +4154,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>16</v>
@@ -4175,7 +4196,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -4187,15 +4208,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4210,7 +4231,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4225,7 +4246,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -4243,7 +4264,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4255,17 +4276,17 @@
         <v>48</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="K71" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4295,7 +4316,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4307,7 +4328,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>74</v>
@@ -4315,7 +4336,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4330,7 +4351,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4342,7 +4363,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J74" s="7">
         <v>169</v>
@@ -4350,7 +4371,7 @@
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4365,7 +4386,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4380,14 +4401,14 @@
         <v>60</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="K75" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4402,7 +4423,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4414,17 +4435,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="K76" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4439,7 +4460,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4451,7 +4472,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J77" s="7">
         <v>102</v>
@@ -4472,7 +4493,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4484,7 +4505,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>122</v>
@@ -4520,7 +4541,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4529,10 +4550,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>50</v>
@@ -4540,7 +4561,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4555,13 +4576,13 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>16</v>
@@ -4575,7 +4596,7 @@
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4590,7 +4611,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4599,20 +4620,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="K82" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4627,29 +4648,29 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="K83" s="7">
         <v>76</v>
       </c>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4664,7 +4685,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4673,13 +4694,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4699,13 +4720,13 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>16</v>
@@ -4714,7 +4735,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4732,7 +4753,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4741,13 +4762,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I86" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4765,22 +4786,22 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4798,7 +4819,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4813,7 +4834,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4846,7 +4867,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4858,17 +4879,17 @@
         <v>121</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>156</v>
       </c>
       <c t="s" r="K90" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4883,7 +4904,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4895,14 +4916,16 @@
         <v>55</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>87</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
-      <c r="M91" s="7"/>
+      <c t="s" r="M91" s="7">
+        <v>224</v>
+      </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c t="s" r="A92" s="6">
@@ -4916,7 +4939,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4928,7 +4951,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>66</v>
@@ -4964,7 +4987,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4979,7 +5002,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4999,7 +5022,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5034,7 +5057,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5052,11 +5075,11 @@
         <v>90</v>
       </c>
       <c t="s" r="K96" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5071,7 +5094,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5083,17 +5106,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="K97" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5108,7 +5131,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5117,20 +5140,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>173</v>
       </c>
       <c t="s" r="K98" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5145,29 +5168,29 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="K99" s="7">
         <v>86</v>
       </c>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5182,7 +5205,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5194,17 +5217,17 @@
         <v>55</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="K100" s="7">
         <v>26</v>
       </c>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -5234,7 +5257,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5243,7 +5266,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="I102" s="7">
         <v>72</v>
@@ -5252,11 +5275,11 @@
         <v>123</v>
       </c>
       <c t="s" r="K102" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5271,19 +5294,19 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>94</v>
@@ -5308,7 +5331,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5323,7 +5346,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="K104" s="7">
         <v>129</v>
@@ -5345,7 +5368,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5367,7 +5390,7 @@
       </c>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5397,7 +5420,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5409,17 +5432,17 @@
         <v>42</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="K107" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5434,7 +5457,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5449,10 +5472,10 @@
         <v>18</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="K108" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
@@ -5471,7 +5494,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5480,13 +5503,13 @@
         <v>55</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5506,13 +5529,13 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>55</v>
@@ -5521,12 +5544,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5541,7 +5564,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5550,13 +5573,13 @@
         <v>55</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5574,22 +5597,22 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5622,7 +5645,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5634,7 +5657,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>56</v>
@@ -5657,7 +5680,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5669,15 +5692,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5692,7 +5715,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5704,7 +5727,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>90</v>
@@ -5727,7 +5750,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5739,7 +5762,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>94</v>
@@ -5749,7 +5772,7 @@
       </c>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5764,7 +5787,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5773,17 +5796,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>128</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
-      <c r="M118" s="7"/>
+      <c t="s" r="M118" s="7">
+        <v>62</v>
+      </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c t="s" r="A119" s="6">
@@ -5797,13 +5822,13 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>16</v>
@@ -5812,7 +5837,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5830,7 +5855,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5839,13 +5864,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5863,19 +5888,19 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>102</v>
@@ -5911,7 +5936,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5923,15 +5948,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5946,7 +5971,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5958,7 +5983,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>128</v>
@@ -5981,7 +6006,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5990,10 +6015,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>117</v>
@@ -6014,13 +6039,13 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>16</v>
@@ -6029,7 +6054,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -6062,7 +6087,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6074,7 +6099,7 @@
         <v>134</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>168</v>
@@ -6082,7 +6107,7 @@
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -6097,7 +6122,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6112,12 +6137,12 @@
         <v>76</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6132,7 +6157,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6167,7 +6192,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6179,7 +6204,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>84</v>
@@ -6202,7 +6227,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6214,7 +6239,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>39</v>
@@ -6235,7 +6260,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6250,7 +6275,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -6283,7 +6308,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6292,13 +6317,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6318,13 +6343,13 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>16</v>
@@ -6333,7 +6358,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -6353,7 +6378,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6362,10 +6387,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>37</v>
@@ -6386,19 +6411,19 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>41</v>
@@ -6419,7 +6444,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6434,7 +6459,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6467,27 +6492,27 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6502,7 +6527,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6514,7 +6539,7 @@
         <v>134</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>95</v>
@@ -6522,7 +6547,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6537,7 +6562,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6570,7 +6595,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6579,10 +6604,10 @@
         <v>55</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>26</v>
@@ -6603,19 +6628,19 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>49</v>
@@ -6651,7 +6676,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6660,18 +6685,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I147" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6686,27 +6711,27 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>89</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6721,19 +6746,19 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>19</v>
@@ -6741,7 +6766,7 @@
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6756,13 +6781,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>16</v>
@@ -6771,12 +6796,12 @@
         <v>142</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6791,7 +6816,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6806,11 +6831,13 @@
         <v>145</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
-      <c r="M151" s="7"/>
+      <c t="s" r="M151" s="7">
+        <v>181</v>
+      </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c t="s" r="A152" s="6">
@@ -6824,7 +6851,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6836,10 +6863,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>291</v>
+        <v>224</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6872,7 +6899,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6881,18 +6908,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6907,13 +6934,13 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>16</v>
@@ -6927,7 +6954,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6942,7 +6969,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6951,10 +6978,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>19</v>
@@ -6977,27 +7004,27 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -7012,7 +7039,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -7032,7 +7059,7 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7043,11 +7070,11 @@
         <v>6844</v>
       </c>
       <c t="s" r="C159" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7059,14 +7086,16 @@
         <v>55</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
-      <c r="M159" s="7"/>
+      <c t="s" r="M159" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c t="s" r="A160" s="6">
@@ -7076,11 +7105,11 @@
         <v>6844</v>
       </c>
       <c t="s" r="C160" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7089,20 +7118,20 @@
         <v>55</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="K160" s="7">
         <v>37</v>
       </c>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7113,26 +7142,26 @@
         <v>6845</v>
       </c>
       <c t="s" r="C161" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -7165,13 +7194,13 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>16</v>
@@ -7180,12 +7209,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7200,7 +7229,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7209,17 +7238,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
-      <c r="M164" s="7"/>
+      <c t="s" r="M164" s="7">
+        <v>199</v>
+      </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c t="s" r="A165" s="6">
@@ -7233,22 +7264,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -7281,7 +7312,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7301,7 +7332,7 @@
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7316,7 +7347,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7331,12 +7362,12 @@
         <v>52</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7351,7 +7382,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7366,12 +7397,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7386,7 +7417,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7395,20 +7426,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7423,29 +7454,29 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="K171" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7475,7 +7506,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7484,18 +7515,18 @@
         <v>55</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7510,13 +7541,13 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>55</v>
@@ -7545,7 +7576,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7554,18 +7585,18 @@
         <v>55</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7580,13 +7611,13 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>55</v>
@@ -7600,7 +7631,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7615,7 +7646,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7624,18 +7655,18 @@
         <v>55</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7650,13 +7681,13 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>55</v>
@@ -7683,7 +7714,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7695,14 +7726,18 @@
         <v>68</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>254</v>
-      </c>
-      <c r="K179" s="7"/>
+        <v>256</v>
+      </c>
+      <c t="s" r="K179" s="7">
+        <v>40</v>
+      </c>
       <c r="L179" s="7"/>
-      <c r="M179" s="7"/>
+      <c t="s" r="M179" s="7">
+        <v>238</v>
+      </c>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c t="s" r="A180" s="6">
@@ -7716,7 +7751,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7728,14 +7763,18 @@
         <v>55</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>27</v>
       </c>
-      <c r="K180" s="7"/>
+      <c t="s" r="K180" s="7">
+        <v>148</v>
+      </c>
       <c r="L180" s="7"/>
-      <c r="M180" s="7"/>
+      <c t="s" r="M180" s="7">
+        <v>183</v>
+      </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c t="s" r="A181" s="6">
@@ -7749,7 +7788,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7758,17 +7797,21 @@
         <v>55</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="I181" s="7">
         <v>159</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>329</v>
-      </c>
-      <c r="K181" s="7"/>
+        <v>331</v>
+      </c>
+      <c t="s" r="K181" s="7">
+        <v>332</v>
+      </c>
       <c r="L181" s="7"/>
-      <c r="M181" s="7"/>
+      <c t="s" r="M181" s="7">
+        <v>308</v>
+      </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
       <c r="A182" s="6"/>
@@ -7797,7 +7840,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7806,7 +7849,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>122</v>
@@ -7817,7 +7860,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7832,19 +7875,19 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>90</v>
@@ -7852,7 +7895,7 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7867,7 +7910,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7876,20 +7919,20 @@
         <v>55</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="K185" s="7">
         <v>35</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7904,22 +7947,22 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="K186" s="7">
         <v>128</v>
@@ -7937,11 +7980,11 @@
         <v>6293</v>
       </c>
       <c t="s" r="C187" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7950,7 +7993,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>64</v>
@@ -7970,26 +8013,26 @@
         <v>6294</v>
       </c>
       <c t="s" r="C188" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -8022,7 +8065,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8042,7 +8085,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8057,7 +8100,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8069,7 +8112,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>140</v>
@@ -8077,7 +8120,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8092,7 +8135,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8101,18 +8144,18 @@
         <v>68</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8127,13 +8170,13 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>68</v>
@@ -8142,12 +8185,12 @@
         <v>127</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8162,7 +8205,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8174,17 +8217,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>128</v>
       </c>
       <c t="s" r="K194" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>115</v>
+        <v>25</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8199,7 +8242,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8214,10 +8257,10 @@
         <v>115</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="K195" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
@@ -8236,7 +8279,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8251,14 +8294,14 @@
         <v>101</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="K196" s="7">
-        <v>291</v>
+        <v>224</v>
       </c>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8288,7 +8331,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8303,7 +8346,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -8323,7 +8366,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8332,10 +8375,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>128</v>
@@ -8345,7 +8388,7 @@
       </c>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8360,13 +8403,13 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>16</v>
@@ -8375,14 +8418,14 @@
         <v>129</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="K200" s="7">
         <v>85</v>
       </c>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>291</v>
+        <v>224</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8397,7 +8440,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8406,13 +8449,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -8430,22 +8473,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -8478,7 +8521,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8487,7 +8530,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="I204" s="7">
         <v>90</v>
@@ -8498,7 +8541,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8513,19 +8556,19 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>61</v>
@@ -8533,7 +8576,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8563,7 +8606,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8572,13 +8615,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8598,22 +8641,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8633,7 +8676,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8642,7 +8685,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="I209" s="7">
         <v>169</v>
@@ -8651,11 +8694,11 @@
         <v>156</v>
       </c>
       <c t="s" r="K209" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8670,19 +8713,19 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>85</v>
@@ -8692,7 +8735,7 @@
       </c>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8707,7 +8750,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8719,7 +8762,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>100</v>
@@ -8729,7 +8772,7 @@
       </c>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8759,7 +8802,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8771,15 +8814,15 @@
         <v>55</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8794,7 +8837,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8803,20 +8846,20 @@
         <v>55</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="K214" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8831,27 +8874,27 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8866,7 +8909,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8878,10 +8921,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8914,7 +8957,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8923,18 +8966,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="I218" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8949,27 +8992,27 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8984,7 +9027,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8993,7 +9036,7 @@
         <v>42</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>144</v>
@@ -9004,7 +9047,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9019,22 +9062,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -9067,7 +9110,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9087,7 +9130,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9102,7 +9145,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9114,15 +9157,15 @@
         <v>163</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9137,7 +9180,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9149,14 +9192,16 @@
         <v>55</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
-      <c r="M225" s="7"/>
+      <c t="s" r="M225" s="7">
+        <v>379</v>
+      </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c t="s" r="A226" s="6">
@@ -9170,7 +9215,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9185,7 +9230,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -9218,7 +9263,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9233,12 +9278,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9246,14 +9291,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B229" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c t="s" r="C229" s="7">
         <v>14</v>
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9262,20 +9307,20 @@
         <v>55</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>108</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="K229" s="7">
         <v>108</v>
       </c>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9283,36 +9328,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B230" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="C230" s="7">
         <v>14</v>
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="K230" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9327,7 +9372,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9342,14 +9387,14 @@
         <v>40</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c t="s" r="K231" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9379,7 +9424,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9391,17 +9436,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="K233" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9416,7 +9461,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9428,17 +9473,17 @@
         <v>92</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c t="s" r="K234" s="7">
         <v>22</v>
       </c>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9453,7 +9498,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9468,14 +9513,14 @@
         <v>128</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="K235" s="7">
         <v>84</v>
       </c>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9490,7 +9535,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9499,13 +9544,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9538,7 +9583,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9550,7 +9595,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>74</v>
@@ -9558,7 +9603,7 @@
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9573,7 +9618,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9593,7 +9638,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9608,7 +9653,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9628,7 +9673,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9643,7 +9688,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9652,7 +9697,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>63</v>
@@ -9676,13 +9721,13 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>55</v>
@@ -9724,7 +9769,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9733,18 +9778,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9759,13 +9804,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>16</v>
@@ -9774,12 +9819,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9794,7 +9839,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9803,7 +9848,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I246" s="7">
         <v>168</v>
@@ -9829,27 +9874,27 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9864,7 +9909,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9873,17 +9918,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
-      <c r="M248" s="7"/>
+      <c t="s" r="M248" s="7">
+        <v>404</v>
+      </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
       <c t="s" r="A249" s="6">
@@ -9897,22 +9944,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9930,7 +9977,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9942,17 +9989,17 @@
         <v>55</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="K250" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9967,7 +10014,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9979,10 +10026,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -10015,7 +10062,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10027,7 +10074,7 @@
         <v>134</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>138</v>
@@ -10035,7 +10082,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10050,7 +10097,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10059,18 +10106,18 @@
         <v>134</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>94</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10085,22 +10132,22 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>134</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -10118,7 +10165,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10166,7 +10213,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
@@ -10178,15 +10225,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10201,7 +10248,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -10213,7 +10260,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>90</v>
@@ -10221,7 +10268,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10236,7 +10283,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -10248,10 +10295,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="K260" s="7">
         <v>60</v>
@@ -10273,7 +10320,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
@@ -10295,7 +10342,7 @@
       </c>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10310,7 +10357,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
@@ -10343,7 +10390,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -10355,10 +10402,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -10376,7 +10423,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -10388,10 +10435,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -10424,7 +10471,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10433,10 +10480,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>156</v>
@@ -10444,7 +10491,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10459,13 +10506,13 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>16</v>
@@ -10474,12 +10521,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10494,7 +10541,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10506,7 +10553,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>50</v>
@@ -10542,7 +10589,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10562,7 +10609,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10577,7 +10624,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -10589,15 +10636,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10612,7 +10659,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10621,18 +10668,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>417</v>
+        <v>84</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10647,13 +10694,13 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>16</v>
@@ -10680,7 +10727,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -10692,10 +10739,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10713,7 +10760,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -10728,7 +10775,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10761,7 +10808,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10770,13 +10817,13 @@
         <v>55</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>28</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10796,13 +10843,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>55</v>
@@ -10811,12 +10858,12 @@
         <v>50</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10831,7 +10878,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10843,15 +10890,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10866,7 +10913,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10878,17 +10925,17 @@
         <v>92</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c t="s" r="K280" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10903,7 +10950,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10925,7 +10972,7 @@
       </c>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10940,7 +10987,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10949,20 +10996,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="K282" s="7">
         <v>114</v>
       </c>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10977,13 +11024,13 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>16</v>
@@ -10992,14 +11039,14 @@
         <v>100</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="K283" s="7">
         <v>101</v>
       </c>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11029,27 +11076,27 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11064,7 +11111,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -11073,18 +11120,18 @@
         <v>55</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11099,22 +11146,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -11132,7 +11179,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -11141,13 +11188,13 @@
         <v>55</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -11165,22 +11212,22 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -11213,7 +11260,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11225,15 +11272,15 @@
         <v>134</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11248,7 +11295,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11260,7 +11307,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>58</v>
@@ -11268,7 +11315,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11283,7 +11330,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11295,15 +11342,15 @@
         <v>134</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11318,7 +11365,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11333,7 +11380,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -11366,7 +11413,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11375,10 +11422,10 @@
         <v>55</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>70</v>
@@ -11386,7 +11433,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11401,13 +11448,13 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>55</v>
@@ -11421,7 +11468,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11436,7 +11483,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11445,18 +11492,18 @@
         <v>55</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>166</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11471,13 +11518,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>55</v>
@@ -11491,7 +11538,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11506,7 +11553,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11515,17 +11562,19 @@
         <v>55</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
-      <c r="M300" s="7"/>
+      <c t="s" r="M300" s="7">
+        <v>25</v>
+      </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
       <c t="s" r="A301" s="6">
@@ -11539,22 +11588,22 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11572,7 +11621,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11584,10 +11633,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11620,13 +11669,13 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>55</v>
@@ -11635,7 +11684,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -11655,7 +11704,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11667,10 +11716,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="K305" s="7">
         <v>90</v>
@@ -11692,7 +11741,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11704,13 +11753,13 @@
         <v>55</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>173</v>
       </c>
       <c t="s" r="K306" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
@@ -11729,7 +11778,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11747,11 +11796,11 @@
         <v>116</v>
       </c>
       <c t="s" r="K307" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11766,7 +11815,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11778,17 +11827,17 @@
         <v>55</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>44</v>
       </c>
       <c t="s" r="K308" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11803,7 +11852,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11812,10 +11861,10 @@
         <v>55</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>122</v>
@@ -11851,7 +11900,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11860,10 +11909,10 @@
         <v>55</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>76</v>
@@ -11871,7 +11920,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11886,19 +11935,19 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>36</v>
@@ -11906,7 +11955,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11921,7 +11970,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11930,20 +11979,20 @@
         <v>55</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>196</v>
+        <v>456</v>
       </c>
       <c t="s" r="K313" s="7">
         <v>128</v>
       </c>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>25</v>
+        <v>457</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11958,29 +12007,29 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c t="s" r="K314" s="7">
         <v>100</v>
       </c>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11995,7 +12044,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12010,7 +12059,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -12028,7 +12077,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -12040,10 +12089,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -12076,7 +12125,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -12088,7 +12137,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>52</v>
@@ -12096,7 +12145,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12111,7 +12160,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -12123,15 +12172,15 @@
         <v>92</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12146,7 +12195,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12158,15 +12207,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12181,7 +12230,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -12190,13 +12239,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>169</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -12216,13 +12265,13 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>16</v>
@@ -12231,12 +12280,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12251,7 +12300,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12260,10 +12309,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>128</v>
@@ -12273,7 +12322,7 @@
       </c>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12288,13 +12337,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>16</v>
@@ -12303,7 +12352,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="K324" s="7">
         <v>100</v>
@@ -12325,7 +12374,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12337,13 +12386,13 @@
         <v>68</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="K325" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
@@ -12362,7 +12411,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12374,13 +12423,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="K326" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
@@ -12414,7 +12463,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12426,7 +12475,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>74</v>
@@ -12434,7 +12483,7 @@
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12449,7 +12498,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12461,10 +12510,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -12484,7 +12533,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12496,7 +12545,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>156</v>
@@ -12504,7 +12553,7 @@
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12519,7 +12568,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12538,7 +12587,9 @@
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
-      <c r="M331" s="7"/>
+      <c t="s" r="M331" s="7">
+        <v>468</v>
+      </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
       <c t="s" r="A332" s="6">
@@ -12552,7 +12603,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12564,10 +12615,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12585,7 +12636,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12633,7 +12684,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12648,7 +12699,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="K335" s="7">
         <v>87</v>
@@ -12685,7 +12736,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12697,17 +12748,17 @@
         <v>42</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="K337" s="7">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12722,7 +12773,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12734,17 +12785,17 @@
         <v>55</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>138</v>
       </c>
       <c t="s" r="K338" s="7">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12759,7 +12810,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12774,14 +12825,14 @@
         <v>140</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c t="s" r="K339" s="7">
         <v>20</v>
       </c>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12796,7 +12847,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12808,10 +12859,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="K340" s="7">
         <v>79</v>
@@ -12833,7 +12884,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12842,13 +12893,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12866,19 +12917,19 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>103</v>
@@ -12914,7 +12965,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12923,7 +12974,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I344" s="7">
         <v>28</v>
@@ -12934,7 +12985,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12949,27 +13000,27 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12984,19 +13035,19 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>168</v>
@@ -13004,7 +13055,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13019,13 +13070,13 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>55</v>
@@ -13039,7 +13090,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13054,7 +13105,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -13066,10 +13117,10 @@
         <v>163</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -13087,7 +13138,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -13099,14 +13150,18 @@
         <v>55</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>236</v>
-      </c>
-      <c r="K349" s="7"/>
+        <v>238</v>
+      </c>
+      <c t="s" r="K349" s="7">
+        <v>275</v>
+      </c>
       <c r="L349" s="7"/>
-      <c r="M349" s="7"/>
+      <c t="s" r="M349" s="7">
+        <v>148</v>
+      </c>
     </row>
     <row r="350" ht="15" customHeight="1">
       <c t="s" r="A350" s="6">
@@ -13120,7 +13175,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -13132,17 +13187,17 @@
         <v>42</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>119</v>
       </c>
       <c t="s" r="K350" s="7">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>159</v>
+        <v>51</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13157,7 +13212,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13172,11 +13227,15 @@
         <v>102</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>305</v>
-      </c>
-      <c r="K351" s="7"/>
+        <v>307</v>
+      </c>
+      <c t="s" r="K351" s="7">
+        <v>306</v>
+      </c>
       <c r="L351" s="7"/>
-      <c r="M351" s="7"/>
+      <c t="s" r="M351" s="7">
+        <v>471</v>
+      </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c r="A352" s="6"/>
@@ -13205,7 +13264,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -13214,7 +13273,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>69</v>
@@ -13225,7 +13284,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13240,27 +13299,27 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13275,7 +13334,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13284,18 +13343,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13310,13 +13369,13 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>16</v>
@@ -13325,12 +13384,12 @@
         <v>169</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13345,7 +13404,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13354,7 +13413,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>36</v>
@@ -13367,7 +13426,7 @@
       </c>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13382,13 +13441,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>16</v>
@@ -13397,14 +13456,14 @@
         <v>128</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="K358" s="7">
         <v>115</v>
       </c>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13419,7 +13478,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -13431,17 +13490,17 @@
         <v>55</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>39</v>
       </c>
       <c t="s" r="K359" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13456,7 +13515,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -13468,10 +13527,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -13504,7 +13563,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13519,12 +13578,12 @@
         <v>107</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13539,7 +13598,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13554,10 +13613,10 @@
         <v>140</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="K363" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
@@ -13576,7 +13635,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13588,17 +13647,17 @@
         <v>68</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c t="s" r="K364" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13613,7 +13672,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13625,7 +13684,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>105</v>
@@ -13661,7 +13720,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13673,7 +13732,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>73</v>
@@ -13681,7 +13740,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13696,7 +13755,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13705,18 +13764,18 @@
         <v>78</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13731,13 +13790,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>78</v>
@@ -13746,12 +13805,12 @@
         <v>21</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13766,7 +13825,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13775,18 +13834,18 @@
         <v>78</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I370" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13801,13 +13860,13 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>78</v>
@@ -13816,7 +13875,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13834,7 +13893,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13846,7 +13905,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>28</v>
@@ -13882,7 +13941,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13891,13 +13950,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13917,27 +13976,27 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13952,7 +14011,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13964,7 +14023,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>93</v>
@@ -13974,7 +14033,7 @@
       </c>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13989,7 +14048,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -14001,7 +14060,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>35</v>
@@ -14011,7 +14070,7 @@
       </c>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14026,7 +14085,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14038,10 +14097,10 @@
         <v>134</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>196</v>
+        <v>456</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -14059,7 +14118,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14074,7 +14133,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -14107,7 +14166,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14116,18 +14175,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="I381" s="7">
         <v>105</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14142,27 +14201,27 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14177,7 +14236,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -14186,10 +14245,10 @@
         <v>68</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>22</v>
@@ -14199,7 +14258,7 @@
       </c>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>496</v>
+        <v>503</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14214,19 +14273,19 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>130</v>
@@ -14236,7 +14295,7 @@
       </c>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>180</v>
+        <v>100</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14251,7 +14310,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14260,13 +14319,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -14284,22 +14343,22 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -14332,7 +14391,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -14341,18 +14400,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14367,13 +14426,13 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>16</v>
@@ -14387,7 +14446,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>500</v>
+        <v>507</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14395,14 +14454,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B390" s="7">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14411,7 +14470,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c t="s" r="I390" s="7">
         <v>75</v>
@@ -14432,36 +14491,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B391" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c t="s" r="C391" s="7">
         <v>14</v>
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>61</v>
       </c>
       <c t="s" r="K391" s="7">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>503</v>
+        <v>510</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14469,14 +14528,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B392" s="7">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c t="s" r="C392" s="7">
         <v>14</v>
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14491,14 +14550,14 @@
         <v>63</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="K392" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14528,7 +14587,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14543,12 +14602,12 @@
         <v>137</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>506</v>
+        <v>513</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14563,7 +14622,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14575,17 +14634,17 @@
         <v>42</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="K395" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14600,7 +14659,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14615,14 +14674,14 @@
         <v>166</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="K396" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>508</v>
+        <v>515</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14637,7 +14696,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14649,7 +14708,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>94</v>
@@ -14657,7 +14716,7 @@
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>509</v>
+        <v>516</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14672,7 +14731,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14681,13 +14740,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>114</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14705,13 +14764,13 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>68</v>
@@ -14753,27 +14812,27 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>512</v>
+        <v>519</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14788,7 +14847,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
@@ -14803,7 +14862,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -14821,7 +14880,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -14833,7 +14892,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>44</v>
@@ -14869,19 +14928,19 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>36</v>
@@ -14889,7 +14948,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14904,7 +14963,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -14916,10 +14975,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14930,14 +14989,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B407" s="7">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c t="s" r="C407" s="7">
         <v>14</v>
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -14952,14 +15011,14 @@
         <v>64</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c t="s" r="K407" s="7">
         <v>64</v>
       </c>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14967,14 +15026,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B408" s="7">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c t="s" r="C408" s="7">
         <v>14</v>
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -14986,17 +15045,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c t="s" r="K408" s="7">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -15026,7 +15085,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
@@ -15038,15 +15097,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>520</v>
+        <v>527</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15061,7 +15120,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -15096,7 +15155,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -15105,20 +15164,20 @@
         <v>134</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="K412" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15133,13 +15192,13 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>134</v>
@@ -15148,10 +15207,10 @@
         <v>147</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="K413" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
@@ -15178,14 +15237,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B415" s="7">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c t="s" r="C415" s="7">
         <v>14</v>
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -15197,17 +15256,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="K415" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15215,14 +15274,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B416" s="7">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c t="s" r="C416" s="7">
         <v>14</v>
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -15237,14 +15296,14 @@
         <v>110</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="K416" s="7">
         <v>110</v>
       </c>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>525</v>
+        <v>532</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15252,14 +15311,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B417" s="7">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c t="s" r="C417" s="7">
         <v>14</v>
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -15274,14 +15333,14 @@
         <v>76</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="K417" s="7">
         <v>76</v>
       </c>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15289,14 +15348,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B418" s="7">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c t="s" r="C418" s="7">
         <v>14</v>
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -15308,17 +15367,17 @@
         <v>55</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="K418" s="7">
         <v>113</v>
       </c>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15326,14 +15385,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B419" s="7">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c t="s" r="C419" s="7">
         <v>14</v>
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
@@ -15355,7 +15414,7 @@
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15385,7 +15444,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -15400,14 +15459,14 @@
         <v>166</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="K421" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15422,7 +15481,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -15431,13 +15490,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -15466,11 +15525,11 @@
         <v>6874</v>
       </c>
       <c t="s" r="C424" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
@@ -15479,10 +15538,10 @@
         <v>134</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>41</v>
@@ -15490,7 +15549,7 @@
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -15501,23 +15560,23 @@
         <v>6852</v>
       </c>
       <c t="s" r="C425" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>50</v>
@@ -15553,7 +15612,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
@@ -15562,7 +15621,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c t="s" r="I427" s="7">
         <v>140</v>
@@ -15573,7 +15632,7 @@
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -15588,22 +15647,22 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15611,7 +15670,7 @@
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c t="s" r="A429" s="9">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="B429" s="9"/>
       <c r="C429" s="9"/>
@@ -15631,7 +15690,7 @@
     <row r="430" ht="66" customHeight="1"/>
     <row r="431" ht="16.5" customHeight="1">
       <c t="s" r="A431" s="10">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B431" s="10"/>
       <c r="C431" s="10"/>
@@ -15644,7 +15703,7 @@
       <c r="J431" s="10"/>
       <c r="K431" s="10"/>
       <c t="s" r="L431" s="11">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="M431" s="11"/>
       <c r="N431" s="11"/>
